--- a/data/cepea-consulta-dolar.reparado.xlsx
+++ b/data/cepea-consulta-dolar.reparado.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipe.guidastri\Documents\Projetos\painel-controle-commodities\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipe.guidastri\Documents\Projetos\acompanhamento-cotacao\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F2B30221-8AA3-4F5B-B0BF-DD9AB684BE9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{88A06A75-F21E-4831-82B4-BDEBB778CCA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5760" yWindow="3396" windowWidth="17280" windowHeight="8964"/>
   </bookViews>

--- a/data/cepea-consulta-dolar.reparado.xlsx
+++ b/data/cepea-consulta-dolar.reparado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipe.guidastri\Documents\Projetos\acompanhamento-cotacao\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{88A06A75-F21E-4831-82B4-BDEBB778CCA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B06775F-6F5F-4F99-9171-450095004DA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="3396" windowWidth="17280" windowHeight="8964"/>
+    <workbookView xWindow="3240" yWindow="2052" windowWidth="17280" windowHeight="8964"/>
   </bookViews>
   <sheets>
     <sheet name="Plan 1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="533">
   <si>
     <t>Dólar | Dólar</t>
   </si>
@@ -1609,6 +1609,27 @@
   </si>
   <si>
     <t>5,40</t>
+  </si>
+  <si>
+    <t>14/08/2025</t>
+  </si>
+  <si>
+    <t>15/08/2025</t>
+  </si>
+  <si>
+    <t>18/08/2025</t>
+  </si>
+  <si>
+    <t>19/08/2025</t>
+  </si>
+  <si>
+    <t>20/08/2025</t>
+  </si>
+  <si>
+    <t>21/08/2025</t>
+  </si>
+  <si>
+    <t>22/08/2025</t>
   </si>
 </sst>
 </file>
@@ -2060,7 +2081,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J409"/>
+  <dimension ref="A1:J416"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" customWidth="1"/>
@@ -5343,6 +5364,62 @@
       </c>
       <c r="B409" s="3" t="s">
         <v>525</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A410" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="B410" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A411" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="B411" s="3" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A412" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="B412" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A413" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="B413" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A414" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="B414" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A415" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="B415" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A416" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="B416" s="3" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/data/cepea-consulta-dolar.reparado.xlsx
+++ b/data/cepea-consulta-dolar.reparado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipe.guidastri\Documents\Projetos\acompanhamento-cotacao\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B06775F-6F5F-4F99-9171-450095004DA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8502DDFE-547D-4BCD-93DF-7C8CD748A665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3240" yWindow="2052" windowWidth="17280" windowHeight="8964"/>
   </bookViews>

--- a/data/cepea-consulta-dolar.reparado.xlsx
+++ b/data/cepea-consulta-dolar.reparado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipe.guidastri\Documents\Projetos\acompanhamento-cotacao\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8502DDFE-547D-4BCD-93DF-7C8CD748A665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{438447B8-E4BD-4C3C-B17B-A9BA7B69EF60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3240" yWindow="2052" windowWidth="17280" windowHeight="8964"/>
+    <workbookView xWindow="5760" yWindow="3396" windowWidth="17280" windowHeight="8964"/>
   </bookViews>
   <sheets>
     <sheet name="Plan 1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="536">
   <si>
     <t>Dólar | Dólar</t>
   </si>
@@ -1630,6 +1630,15 @@
   </si>
   <si>
     <t>22/08/2025</t>
+  </si>
+  <si>
+    <t>25/08/2025</t>
+  </si>
+  <si>
+    <t>26/08/2025</t>
+  </si>
+  <si>
+    <t>27/08/2025</t>
   </si>
 </sst>
 </file>
@@ -2081,7 +2090,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J416"/>
+  <dimension ref="A1:J419"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" customWidth="1"/>
@@ -5420,6 +5429,30 @@
       </c>
       <c r="B416" s="3" t="s">
         <v>167</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A417" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="B417" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A418" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="B418" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A419" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="B419" s="3" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>

--- a/data/cepea-consulta-dolar.reparado.xlsx
+++ b/data/cepea-consulta-dolar.reparado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipe.guidastri\Documents\Projetos\acompanhamento-cotacao\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{438447B8-E4BD-4C3C-B17B-A9BA7B69EF60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E84E27B3-EDC9-45B8-805A-AAF33438BE87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5760" yWindow="3396" windowWidth="17280" windowHeight="8964"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="537">
   <si>
     <t>Dólar | Dólar</t>
   </si>
@@ -1639,6 +1639,9 @@
   </si>
   <si>
     <t>27/08/2025</t>
+  </si>
+  <si>
+    <t>28/08/2025</t>
   </si>
 </sst>
 </file>
@@ -2090,7 +2093,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J419"/>
+  <dimension ref="A1:J420"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" customWidth="1"/>
@@ -5453,6 +5456,14 @@
       </c>
       <c r="B419" s="3" t="s">
         <v>165</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A420" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="B420" s="3" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
